--- a/src/lib/payroll-engine/__fixtures__/edge.xlsx
+++ b/src/lib/payroll-engine/__fixtures__/edge.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="AE2" s="3" t="inlineStr">
         <is>
-          <t>SA1980000495608016363188</t>
+          <t>SA7480000000000000001234</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr">
